--- a/artfynd/A 61693-2025 artfynd.xlsx
+++ b/artfynd/A 61693-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130557519</v>
       </c>
       <c r="B2" t="n">
-        <v>97169</v>
+        <v>97195</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130557524</v>
       </c>
       <c r="B3" t="n">
-        <v>92381</v>
+        <v>92407</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130557520</v>
       </c>
       <c r="B4" t="n">
-        <v>111080</v>
+        <v>111106</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130557522</v>
       </c>
       <c r="B5" t="n">
-        <v>111080</v>
+        <v>111106</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61693-2025 artfynd.xlsx
+++ b/artfynd/A 61693-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130557519</v>
       </c>
       <c r="B2" t="n">
-        <v>97195</v>
+        <v>97196</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130557524</v>
       </c>
       <c r="B3" t="n">
-        <v>92407</v>
+        <v>92408</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130557520</v>
       </c>
       <c r="B4" t="n">
-        <v>111106</v>
+        <v>111107</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130557522</v>
       </c>
       <c r="B5" t="n">
-        <v>111106</v>
+        <v>111107</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61693-2025 artfynd.xlsx
+++ b/artfynd/A 61693-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130557519</v>
       </c>
       <c r="B2" t="n">
-        <v>97196</v>
+        <v>97197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130557524</v>
       </c>
       <c r="B3" t="n">
-        <v>92408</v>
+        <v>92409</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130557520</v>
       </c>
       <c r="B4" t="n">
-        <v>111107</v>
+        <v>111108</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130557522</v>
       </c>
       <c r="B5" t="n">
-        <v>111107</v>
+        <v>111108</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61693-2025 artfynd.xlsx
+++ b/artfynd/A 61693-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130557519</v>
       </c>
       <c r="B2" t="n">
-        <v>97197</v>
+        <v>97199</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130557524</v>
       </c>
       <c r="B3" t="n">
-        <v>92409</v>
+        <v>92411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130557520</v>
       </c>
       <c r="B4" t="n">
-        <v>111108</v>
+        <v>111110</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130557522</v>
       </c>
       <c r="B5" t="n">
-        <v>111108</v>
+        <v>111110</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61693-2025 artfynd.xlsx
+++ b/artfynd/A 61693-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130557519</v>
       </c>
       <c r="B2" t="n">
-        <v>97199</v>
+        <v>97203</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130557524</v>
       </c>
       <c r="B3" t="n">
-        <v>92411</v>
+        <v>92415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130557520</v>
       </c>
       <c r="B4" t="n">
-        <v>111110</v>
+        <v>111114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130557522</v>
       </c>
       <c r="B5" t="n">
-        <v>111110</v>
+        <v>111114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61693-2025 artfynd.xlsx
+++ b/artfynd/A 61693-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130557519</v>
       </c>
       <c r="B2" t="n">
-        <v>97203</v>
+        <v>97216</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130557524</v>
       </c>
       <c r="B3" t="n">
-        <v>92415</v>
+        <v>92428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130557520</v>
       </c>
       <c r="B4" t="n">
-        <v>111114</v>
+        <v>111127</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130557522</v>
       </c>
       <c r="B5" t="n">
-        <v>111114</v>
+        <v>111127</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61693-2025 artfynd.xlsx
+++ b/artfynd/A 61693-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130557519</v>
       </c>
       <c r="B2" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130557524</v>
       </c>
       <c r="B3" t="n">
-        <v>92428</v>
+        <v>92429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130557520</v>
       </c>
       <c r="B4" t="n">
-        <v>111127</v>
+        <v>111128</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130557522</v>
       </c>
       <c r="B5" t="n">
-        <v>111127</v>
+        <v>111128</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61693-2025 artfynd.xlsx
+++ b/artfynd/A 61693-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130557519</v>
       </c>
       <c r="B2" t="n">
-        <v>97217</v>
+        <v>97220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130557524</v>
       </c>
       <c r="B3" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130557520</v>
       </c>
       <c r="B4" t="n">
-        <v>111128</v>
+        <v>111131</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130557522</v>
       </c>
       <c r="B5" t="n">
-        <v>111128</v>
+        <v>111131</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61693-2025 artfynd.xlsx
+++ b/artfynd/A 61693-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130557519</v>
       </c>
       <c r="B2" t="n">
-        <v>97220</v>
+        <v>97229</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130557524</v>
       </c>
       <c r="B3" t="n">
-        <v>92430</v>
+        <v>92438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130557520</v>
       </c>
       <c r="B4" t="n">
-        <v>111131</v>
+        <v>111145</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130557522</v>
       </c>
       <c r="B5" t="n">
-        <v>111131</v>
+        <v>111145</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61693-2025 artfynd.xlsx
+++ b/artfynd/A 61693-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>130557520</v>
       </c>
       <c r="B4" t="n">
-        <v>111145</v>
+        <v>111183</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130557522</v>
       </c>
       <c r="B5" t="n">
-        <v>111145</v>
+        <v>111183</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61693-2025 artfynd.xlsx
+++ b/artfynd/A 61693-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130557519</v>
       </c>
       <c r="B2" t="n">
-        <v>97249</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130557524</v>
       </c>
       <c r="B3" t="n">
-        <v>92458</v>
+        <v>92564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,11 +872,11 @@
         <v>130557520</v>
       </c>
       <c r="B4" t="n">
-        <v>111223</v>
+        <v>111389</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -969,11 +969,11 @@
         <v>130557522</v>
       </c>
       <c r="B5" t="n">
-        <v>111223</v>
+        <v>111389</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">

--- a/artfynd/A 61693-2025 artfynd.xlsx
+++ b/artfynd/A 61693-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130557519</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130557524</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130557520</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,8 +1080,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130557522</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>